--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_1.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_1.xlsx
@@ -658,7 +658,7 @@
         <v>0.008446913970685845</v>
       </c>
       <c r="C2" t="n">
-        <v>80766036</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>80766036</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>53998969</v>
+        <v>4902950</v>
       </c>
       <c r="L2" t="n">
-        <v>30159157</v>
+        <v>3206462</v>
       </c>
       <c r="M2" t="n">
-        <v>7431057</v>
+        <v>906185</v>
       </c>
       <c r="N2" t="n">
-        <v>401709</v>
+        <v>68563</v>
       </c>
       <c r="O2" t="n">
-        <v>4499690</v>
+        <v>507877</v>
       </c>
       <c r="P2" t="n">
-        <v>1851009</v>
+        <v>192214</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999053478240967</v>
+        <v>0.9999983906745911</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8468310832977295</v>
+        <v>0.9994675517082214</v>
       </c>
       <c r="S2" t="n">
-        <v>0.710439920425415</v>
+        <v>0.9849804639816284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6238771080970764</v>
+        <v>0.9791979193687439</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4544666707515717</v>
+        <v>0.9925877451896667</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6791895627975464</v>
+        <v>0.9963530302047729</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7391868829727173</v>
+        <v>0.9987581372261047</v>
       </c>
       <c r="X2" t="n">
-        <v>80766036</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>80766036</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>52704308</v>
+        <v>4722285</v>
       </c>
       <c r="AG2" t="n">
-        <v>27993889</v>
+        <v>2920052</v>
       </c>
       <c r="AH2" t="n">
-        <v>6763337</v>
+        <v>795698</v>
       </c>
       <c r="AI2" t="n">
-        <v>369075</v>
+        <v>58613</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4143173</v>
+        <v>458430</v>
       </c>
       <c r="AK2" t="n">
-        <v>1741100</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8210596442222595</v>
+        <v>0.9563660621643066</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.672071635723114</v>
+        <v>0.911352276802063</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5617667436599731</v>
+        <v>0.8591848611831665</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3212381303310394</v>
+        <v>0.6632080674171448</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6273065805435181</v>
+        <v>0.9023253321647644</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6929974555969238</v>
+        <v>0.931419849395752</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027698497621615</v>
       </c>
       <c r="C3" t="n">
-        <v>2459</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>53998969</v>
+        <v>4902950</v>
       </c>
       <c r="E3" t="n">
-        <v>8761970</v>
+        <v>28002</v>
       </c>
       <c r="F3" t="n">
-        <v>524651</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>60586</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>54378</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>8929</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>128141517</v>
+        <v>9857618</v>
       </c>
       <c r="K3" t="n">
-        <v>135736298</v>
+        <v>11136826</v>
       </c>
       <c r="L3" t="n">
-        <v>154327336</v>
+        <v>12812141</v>
       </c>
       <c r="M3" t="n">
-        <v>192296527</v>
+        <v>15123969</v>
       </c>
       <c r="N3" t="n">
-        <v>207276791</v>
+        <v>15981420</v>
       </c>
       <c r="O3" t="n">
-        <v>200158922</v>
+        <v>15560151</v>
       </c>
       <c r="P3" t="n">
-        <v>205746236</v>
+        <v>15876898</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8515583276748657</v>
+        <v>0.9943191409111023</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7130559682846069</v>
+        <v>0.9990954399108887</v>
       </c>
       <c r="T3" t="n">
-        <v>0.612182080745697</v>
+        <v>0.9773560762405396</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3474375307559967</v>
+        <v>0.7750033736228943</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6785960793495178</v>
+        <v>0.9989909529685974</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7357366681098938</v>
+        <v>0.9945721626281738</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52704308</v>
+        <v>4722285</v>
       </c>
       <c r="Z3" t="n">
-        <v>9716599</v>
+        <v>193720</v>
       </c>
       <c r="AA3" t="n">
-        <v>708597</v>
+        <v>8247</v>
       </c>
       <c r="AB3" t="n">
-        <v>197787</v>
+        <v>6669</v>
       </c>
       <c r="AC3" t="n">
-        <v>71596</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>13055</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>128149164</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>134016972</v>
+        <v>10923985</v>
       </c>
       <c r="AG3" t="n">
-        <v>152960319</v>
+        <v>12577000</v>
       </c>
       <c r="AH3" t="n">
-        <v>191500494</v>
+        <v>15012810</v>
       </c>
       <c r="AI3" t="n">
-        <v>206979156</v>
+        <v>15952167</v>
       </c>
       <c r="AJ3" t="n">
-        <v>199822790</v>
+        <v>15512386</v>
       </c>
       <c r="AK3" t="n">
-        <v>205628023</v>
+        <v>15863883</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8311416506767273</v>
+        <v>0.9576802849769592</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.661862313747406</v>
+        <v>0.9098535180091858</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5571742653846741</v>
+        <v>0.8581914901733398</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3192124366760254</v>
+        <v>0.6625333428382874</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6248299479484558</v>
+        <v>0.9017289876937866</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6920501589775085</v>
+        <v>0.931419849395752</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03195506504971016</v>
       </c>
       <c r="C4" t="n">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8997428</v>
+        <v>2399</v>
       </c>
       <c r="E4" t="n">
-        <v>30159157</v>
+        <v>3206462</v>
       </c>
       <c r="F4" t="n">
-        <v>2539526</v>
+        <v>498</v>
       </c>
       <c r="G4" t="n">
-        <v>108724</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>424203</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>65652</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7647</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>9766960</v>
+        <v>2612</v>
       </c>
       <c r="L4" t="n">
-        <v>12292225</v>
+        <v>48894</v>
       </c>
       <c r="M4" t="n">
-        <v>4480034</v>
+        <v>19251</v>
       </c>
       <c r="N4" t="n">
-        <v>482204</v>
+        <v>512</v>
       </c>
       <c r="O4" t="n">
-        <v>2125397</v>
+        <v>1859</v>
       </c>
       <c r="P4" t="n">
-        <v>653106</v>
+        <v>239</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999526739120483</v>
+        <v>0.9999992251396179</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8491881489753723</v>
+        <v>0.9968867301940918</v>
       </c>
       <c r="S4" t="n">
-        <v>0.71174556016922</v>
+        <v>0.9919877648353577</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6179742813110352</v>
+        <v>0.9782761931419373</v>
       </c>
       <c r="U4" t="n">
-        <v>0.393809586763382</v>
+        <v>0.8704036474227905</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6788926720619202</v>
+        <v>0.9976702928543091</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374577522277832</v>
+        <v>0.9966607689857483</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>10517403</v>
+        <v>201254</v>
       </c>
       <c r="Z4" t="n">
-        <v>27993889</v>
+        <v>2920052</v>
       </c>
       <c r="AA4" t="n">
-        <v>2988805</v>
+        <v>81460</v>
       </c>
       <c r="AB4" t="n">
-        <v>204219</v>
+        <v>5413</v>
       </c>
       <c r="AC4" t="n">
-        <v>508341</v>
+        <v>1118</v>
       </c>
       <c r="AD4" t="n">
-        <v>82982</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>11486286</v>
+        <v>215453</v>
       </c>
       <c r="AG4" t="n">
-        <v>13659242</v>
+        <v>284035</v>
       </c>
       <c r="AH4" t="n">
-        <v>5276067</v>
+        <v>130410</v>
       </c>
       <c r="AI4" t="n">
-        <v>779839</v>
+        <v>29765</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2461529</v>
+        <v>49624</v>
       </c>
       <c r="AK4" t="n">
-        <v>771319</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8260698914527893</v>
+        <v>0.9570227265357971</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6669278740882874</v>
+        <v>0.9106022119522095</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5594610571861267</v>
+        <v>0.8586879372596741</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3202220499515533</v>
+        <v>0.6628705263137817</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6260658502578735</v>
+        <v>0.9020271301269531</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6925234198570251</v>
+        <v>0.931419849395752</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>550488</v>
+        <v>138</v>
       </c>
       <c r="E5" t="n">
-        <v>2800843</v>
+        <v>20634</v>
       </c>
       <c r="F5" t="n">
-        <v>7431057</v>
+        <v>906185</v>
       </c>
       <c r="G5" t="n">
-        <v>171118</v>
+        <v>217</v>
       </c>
       <c r="H5" t="n">
-        <v>1029882</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>153801</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9412973</v>
+        <v>28012</v>
       </c>
       <c r="L5" t="n">
-        <v>12136482</v>
+        <v>2903</v>
       </c>
       <c r="M5" t="n">
-        <v>4707582</v>
+        <v>20995</v>
       </c>
       <c r="N5" t="n">
-        <v>754496</v>
+        <v>19905</v>
       </c>
       <c r="O5" t="n">
-        <v>2131191</v>
+        <v>513</v>
       </c>
       <c r="P5" t="n">
-        <v>664849</v>
+        <v>1049</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999634027481079</v>
+        <v>0.9999994039535522</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9081927537918091</v>
+        <v>0.998094379901886</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8830687999725342</v>
+        <v>0.9967768788337708</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9560222625732422</v>
+        <v>0.9974956512451172</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9940803647041321</v>
+        <v>0.9987295269966125</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9796252846717834</v>
+        <v>0.9998524188995361</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936914443969727</v>
+        <v>0.9999198317527771</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>693093</v>
+        <v>7807</v>
       </c>
       <c r="Z5" t="n">
-        <v>3101842</v>
+        <v>84176</v>
       </c>
       <c r="AA5" t="n">
-        <v>6763337</v>
+        <v>795698</v>
       </c>
       <c r="AB5" t="n">
-        <v>211857</v>
+        <v>9870</v>
       </c>
       <c r="AC5" t="n">
-        <v>1184653</v>
+        <v>28996</v>
       </c>
       <c r="AD5" t="n">
-        <v>183857</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>10707634</v>
+        <v>208677</v>
       </c>
       <c r="AG5" t="n">
-        <v>14301750</v>
+        <v>289313</v>
       </c>
       <c r="AH5" t="n">
-        <v>5375302</v>
+        <v>131482</v>
       </c>
       <c r="AI5" t="n">
-        <v>787130</v>
+        <v>29855</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2487708</v>
+        <v>49960</v>
       </c>
       <c r="AK5" t="n">
-        <v>774758</v>
+        <v>13254</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8937658667564392</v>
+        <v>0.9736080169677734</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.866161048412323</v>
+        <v>0.9643227458000183</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9490157961845398</v>
+        <v>0.9837034344673157</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9924994707107544</v>
+        <v>0.9962900876998901</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9763098359107971</v>
+        <v>0.9938032627105713</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9925994873046875</v>
+        <v>0.9983505010604858</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1881</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>152467</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
-        <v>210657</v>
+        <v>258</v>
       </c>
       <c r="F6" t="n">
-        <v>235160</v>
+        <v>18725</v>
       </c>
       <c r="G6" t="n">
-        <v>401709</v>
+        <v>68563</v>
       </c>
       <c r="H6" t="n">
-        <v>130222</v>
+        <v>837</v>
       </c>
       <c r="I6" t="n">
-        <v>24109</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>181899</v>
+        <v>6357</v>
       </c>
       <c r="Z6" t="n">
-        <v>214867</v>
+        <v>5249</v>
       </c>
       <c r="AA6" t="n">
-        <v>216558</v>
+        <v>10819</v>
       </c>
       <c r="AB6" t="n">
-        <v>369075</v>
+        <v>58613</v>
       </c>
       <c r="AC6" t="n">
-        <v>146121</v>
+        <v>6949</v>
       </c>
       <c r="AD6" t="n">
-        <v>27685</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>61998</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>467970</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1077539</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>122478</v>
+        <v>273</v>
       </c>
       <c r="H7" t="n">
-        <v>4499690</v>
+        <v>507877</v>
       </c>
       <c r="I7" t="n">
-        <v>400615</v>
+        <v>229</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>86218</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>561941</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>1233443</v>
+        <v>29554</v>
       </c>
       <c r="AB7" t="n">
-        <v>142366</v>
+        <v>7548</v>
       </c>
       <c r="AC7" t="n">
-        <v>4143173</v>
+        <v>458430</v>
       </c>
       <c r="AD7" t="n">
-        <v>463740</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>317</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>4579</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>50785</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>103158</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>19298</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>486712</v>
+        <v>1016</v>
       </c>
       <c r="I8" t="n">
-        <v>1851009</v>
+        <v>192214</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7673</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>63993</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>128664</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>23610</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>550818</v>
+        <v>12550</v>
       </c>
       <c r="AD8" t="n">
-        <v>1741100</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
